--- a/dama/cases/营收系统数据标准/2 服务类/2.4 业务交易数据/2.4.2 收费信息/14. 收费汇总.xlsx
+++ b/dama/cases/营收系统数据标准/2 服务类/2.4 业务交易数据/2.4.2 收费信息/14. 收费汇总.xlsx
@@ -7,14 +7,14 @@
     <workbookView windowWidth="28800" windowHeight="12540"/>
   </bookViews>
   <sheets>
-    <sheet name="收费信息" sheetId="1" r:id="rId1"/>
+    <sheet name="收费汇总表数据标准" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1551" uniqueCount="319">
   <si>
     <t>业务属性</t>
   </si>
@@ -235,7 +235,7 @@
     <t>收费信息</t>
   </si>
   <si>
-    <t>收费汇总记录的唯一标识编号</t>
+    <t>收费汇总编号的唯一标识</t>
   </si>
   <si>
     <t>系统生成，唯一不可重复，非空</t>
@@ -265,15 +265,12 @@
     <t>不可销毁</t>
   </si>
   <si>
-    <t>不销毁，仅通过业务状态标记停用</t>
+    <t>不执行销毁，仅通过业务状态标记停用</t>
   </si>
   <si>
     <t>仅允许数字</t>
   </si>
   <si>
-    <t>唯一编码</t>
-  </si>
-  <si>
     <t>是</t>
   </si>
   <si>
@@ -292,7 +289,7 @@
     <t>SUBCOM_CODE</t>
   </si>
   <si>
-    <t>收费站点的编码标识</t>
+    <t>标识站点业务信息</t>
   </si>
   <si>
     <t>允许为空</t>
@@ -304,10 +301,10 @@
     <t>文本</t>
   </si>
   <si>
-    <t>支持中文、自由文本</t>
-  </si>
-  <si>
-    <t>关联站点表-CSM_SUBCOMPANIES</t>
+    <t>支持中文自由文本</t>
+  </si>
+  <si>
+    <t>自由文本</t>
   </si>
   <si>
     <t>否</t>
@@ -322,7 +319,7 @@
     <t>CMP_ACCOUNT_ID</t>
   </si>
   <si>
-    <t>水司账户的标识编号</t>
+    <t>水司账户的唯一标识</t>
   </si>
   <si>
     <t>非空</t>
@@ -337,7 +334,7 @@
     <t>CASHIER</t>
   </si>
   <si>
-    <t>收费员的标识编号</t>
+    <t>标识收费员业务信息</t>
   </si>
   <si>
     <t>RCM_START_TIME</t>
@@ -349,7 +346,7 @@
     <t>START_TIME</t>
   </si>
   <si>
-    <t>收费汇总周期的开始时间</t>
+    <t>记录业务开始时间</t>
   </si>
   <si>
     <t>DATE</t>
@@ -361,7 +358,7 @@
     <t>日期时间格式</t>
   </si>
   <si>
-    <t>标准日期时间</t>
+    <t>标准时间</t>
   </si>
   <si>
     <t>RCM_END_TIME</t>
@@ -373,7 +370,7 @@
     <t>END_TIME</t>
   </si>
   <si>
-    <t>收费汇总周期的结束时间</t>
+    <t>记录业务结束时间</t>
   </si>
   <si>
     <t>RCM_PT_TOTAL_NUM</t>
@@ -385,7 +382,7 @@
     <t>PT_TOTAL_NUM</t>
   </si>
   <si>
-    <t>收费汇总的总笔数</t>
+    <t>标识总数业务信息</t>
   </si>
   <si>
     <t>笔</t>
@@ -400,7 +397,7 @@
     <t>PT_TOTAL_MONEY</t>
   </si>
   <si>
-    <t>收费汇总的总金额</t>
+    <t>记录总金额数据</t>
   </si>
   <si>
     <t>元</t>
@@ -415,7 +412,7 @@
     <t>PT_CASH_NUM</t>
   </si>
   <si>
-    <t>现金收费的笔数</t>
+    <t>记录现金笔数统计值</t>
   </si>
   <si>
     <t>RCM_PT_CASH_MONEY</t>
@@ -427,7 +424,7 @@
     <t>PT_CASH_MONEY</t>
   </si>
   <si>
-    <t>现金收费的金额</t>
+    <t>记录现金金额数据</t>
   </si>
   <si>
     <t>RCM_PT_POS_NUM</t>
@@ -439,7 +436,7 @@
     <t>PT_POS_NUM</t>
   </si>
   <si>
-    <t>POS收费的笔数</t>
+    <t>记录POS笔数统计值</t>
   </si>
   <si>
     <t>RCM_PT_POS_MONEY</t>
@@ -451,7 +448,7 @@
     <t>PT_POS_MONEY</t>
   </si>
   <si>
-    <t>POS收费的金额</t>
+    <t>记录POS金额数据</t>
   </si>
   <si>
     <t>RCM_PT_CHEQUE_NUM</t>
@@ -463,7 +460,7 @@
     <t>PT_CHEQUE_NUM</t>
   </si>
   <si>
-    <t>支票收费的笔数</t>
+    <t>记录支票笔数统计值</t>
   </si>
   <si>
     <t>RCM_PT_CHEQUE_MONEY</t>
@@ -475,7 +472,7 @@
     <t>PT_CHEQUE_MONEY</t>
   </si>
   <si>
-    <t>支票收费的金额</t>
+    <t>记录支票金额数据</t>
   </si>
   <si>
     <t>RCM_PT_VOUCHER_NUM</t>
@@ -487,7 +484,7 @@
     <t>PT_VOUCHER_NUM</t>
   </si>
   <si>
-    <t>回执收费的笔数</t>
+    <t>记录回执笔数统计值</t>
   </si>
   <si>
     <t>RCM_PT_VOUCHER_MONEY</t>
@@ -499,7 +496,7 @@
     <t>PT_VOUCHER_MONEY</t>
   </si>
   <si>
-    <t>回执收费的金额</t>
+    <t>记录回执金额数据</t>
   </si>
   <si>
     <t>RCM_PT_NORMAL_NUM</t>
@@ -511,7 +508,469 @@
     <t>PT_NORMAL_NUM</t>
   </si>
   <si>
-    <t>正常收费的笔数</t>
+    <t>记录正常笔数统计值</t>
+  </si>
+  <si>
+    <t>RCM_PT_NORMAL_MONEY</t>
+  </si>
+  <si>
+    <t>正常金额</t>
+  </si>
+  <si>
+    <t>PT_NORMAL_MONEY</t>
+  </si>
+  <si>
+    <t>记录正常金额数据</t>
+  </si>
+  <si>
+    <t>RCM_PT_REPETITION_NUM</t>
+  </si>
+  <si>
+    <t>重笔笔数</t>
+  </si>
+  <si>
+    <t>PT_REPETITION_NUM</t>
+  </si>
+  <si>
+    <t>记录重笔笔数统计值</t>
+  </si>
+  <si>
+    <t>RCM_PT_REPETITION_MONEY</t>
+  </si>
+  <si>
+    <t>重笔金额</t>
+  </si>
+  <si>
+    <t>PT_REPETITION_MONEY</t>
+  </si>
+  <si>
+    <t>记录重笔金额数据</t>
+  </si>
+  <si>
+    <t>RCM_PT_PUZZLE_NUM</t>
+  </si>
+  <si>
+    <t>疑难笔数</t>
+  </si>
+  <si>
+    <t>PT_PUZZLE_NUM</t>
+  </si>
+  <si>
+    <t>记录疑难笔数统计值</t>
+  </si>
+  <si>
+    <t>RCM_PT_PUZZLE_MONEY</t>
+  </si>
+  <si>
+    <t>疑难金额</t>
+  </si>
+  <si>
+    <t>PT_PUZZLE_MONEY</t>
+  </si>
+  <si>
+    <t>记录疑难金额数据</t>
+  </si>
+  <si>
+    <t>RCM_PT_REFUND_NUM</t>
+  </si>
+  <si>
+    <t>退款笔数</t>
+  </si>
+  <si>
+    <t>PT_REFUND_NUM</t>
+  </si>
+  <si>
+    <t>记录退款笔数统计值</t>
+  </si>
+  <si>
+    <t>RCM_PT_REFUND_MONEY</t>
+  </si>
+  <si>
+    <t>退款金额</t>
+  </si>
+  <si>
+    <t>PT_REFUND_MONEY</t>
+  </si>
+  <si>
+    <t>记录退款金额数据</t>
+  </si>
+  <si>
+    <t>RCM_PT_PRESTORE_IN_NUM</t>
+  </si>
+  <si>
+    <t>预存收款笔数</t>
+  </si>
+  <si>
+    <t>PT_PRESTORE_IN_NUM</t>
+  </si>
+  <si>
+    <t>记录预存收款笔数统计值</t>
+  </si>
+  <si>
+    <t>RCM_PT_PRESTORE_IN_MONEY</t>
+  </si>
+  <si>
+    <t>预存收款金额</t>
+  </si>
+  <si>
+    <t>PT_PRESTORE_IN_MONEY</t>
+  </si>
+  <si>
+    <t>记录预存收款金额数据</t>
+  </si>
+  <si>
+    <t>RCM_PT_PRESTORE_OUT_NUM</t>
+  </si>
+  <si>
+    <t>预付款笔数</t>
+  </si>
+  <si>
+    <t>PT_PRESTORE_OUT_NUM</t>
+  </si>
+  <si>
+    <t>记录预付款笔数统计值</t>
+  </si>
+  <si>
+    <t>RCM_PT_PRESTORE_OUT_MONEY</t>
+  </si>
+  <si>
+    <t>预付款金额</t>
+  </si>
+  <si>
+    <t>PT_PRESTORE_OUT_MONEY</t>
+  </si>
+  <si>
+    <t>记录预付款金额数据</t>
+  </si>
+  <si>
+    <t>RCM_PT_BALANCE_NUM</t>
+  </si>
+  <si>
+    <t>差额笔数</t>
+  </si>
+  <si>
+    <t>PT_BALANCE_NUM</t>
+  </si>
+  <si>
+    <t>记录差额笔数统计值</t>
+  </si>
+  <si>
+    <t>RCM_PT_BALANCE_MONEY</t>
+  </si>
+  <si>
+    <t>差额金额</t>
+  </si>
+  <si>
+    <t>PT_BALANCE_MONEY</t>
+  </si>
+  <si>
+    <t>记录差额金额数据</t>
+  </si>
+  <si>
+    <t>RCM_PT_TEMPORARY_NUM</t>
+  </si>
+  <si>
+    <t>待账笔数</t>
+  </si>
+  <si>
+    <t>PT_TEMPORARY_NUM</t>
+  </si>
+  <si>
+    <t>记录待账笔数统计值</t>
+  </si>
+  <si>
+    <t>RCM_PT_TEMPORARY_MONEY</t>
+  </si>
+  <si>
+    <t>待账金额</t>
+  </si>
+  <si>
+    <t>PT_TEMPORARY_MONEY</t>
+  </si>
+  <si>
+    <t>记录待账金额数据</t>
+  </si>
+  <si>
+    <t>RCM_PT_LATEFEE_NUM</t>
+  </si>
+  <si>
+    <t>违约金笔数</t>
+  </si>
+  <si>
+    <t>PT_LATEFEE_NUM</t>
+  </si>
+  <si>
+    <t>记录违约金笔数统计值</t>
+  </si>
+  <si>
+    <t>RCM_PT_LATEFEE</t>
+  </si>
+  <si>
+    <t>违约金金额</t>
+  </si>
+  <si>
+    <t>PT_LATEFEE</t>
+  </si>
+  <si>
+    <t>记录违约金金额数据</t>
+  </si>
+  <si>
+    <t>RCM_PT_STATE</t>
+  </si>
+  <si>
+    <t>状态（详见收费汇总状态表）</t>
+  </si>
+  <si>
+    <t>PT_STATE</t>
+  </si>
+  <si>
+    <t>标识状态（详见收费汇总状态表）业务信息</t>
+  </si>
+  <si>
+    <t>取值以状态字典为准，不允许为空</t>
+  </si>
+  <si>
+    <t>关联状态字典</t>
+  </si>
+  <si>
+    <t>RCM_CHECKOUT_TIME</t>
+  </si>
+  <si>
+    <t>结账时间</t>
+  </si>
+  <si>
+    <t>CHECKOUT_TIME</t>
+  </si>
+  <si>
+    <t>记录业务结账时间</t>
+  </si>
+  <si>
+    <t>RCM_CHECKOUT_DATE</t>
+  </si>
+  <si>
+    <t>结账日期</t>
+  </si>
+  <si>
+    <t>CHECKOUT_DATE</t>
+  </si>
+  <si>
+    <t>记录业务结账日期</t>
+  </si>
+  <si>
+    <t>RCM_PT_VERFIED_DATE</t>
+  </si>
+  <si>
+    <t>核销时间</t>
+  </si>
+  <si>
+    <t>PT_VERFIED_DATE</t>
+  </si>
+  <si>
+    <t>记录业务核销时间</t>
+  </si>
+  <si>
+    <t>RCM_PT_VERFIER</t>
+  </si>
+  <si>
+    <t>核销人</t>
+  </si>
+  <si>
+    <t>PT_VERFIER</t>
+  </si>
+  <si>
+    <t>标识核销人业务信息</t>
+  </si>
+  <si>
+    <t>RCM_CREATE_DATE</t>
+  </si>
+  <si>
+    <t>创建时间</t>
+  </si>
+  <si>
+    <t>CREATE_DATE</t>
+  </si>
+  <si>
+    <t>记录业务创建时间</t>
+  </si>
+  <si>
+    <t>RCM_CREATE_TIME</t>
+  </si>
+  <si>
+    <t>创建时间戳</t>
+  </si>
+  <si>
+    <t>CREATE_TIME</t>
+  </si>
+  <si>
+    <t>记录业务创建时间戳</t>
+  </si>
+  <si>
+    <t>RCM_PT_F2F_ALIPAY_MONEY</t>
+  </si>
+  <si>
+    <t>支付宝金额（当面付）</t>
+  </si>
+  <si>
+    <t>PT_F2F_ALIPAY_MONEY</t>
+  </si>
+  <si>
+    <t>记录支付宝金额（当面付）数据</t>
+  </si>
+  <si>
+    <t>RCM_PT_F2F_WECHAT_MONEY</t>
+  </si>
+  <si>
+    <t>微信支付金额（当面付）</t>
+  </si>
+  <si>
+    <t>PT_F2F_WECHAT_MONEY</t>
+  </si>
+  <si>
+    <t>记录微信支付金额（当面付）数据</t>
+  </si>
+  <si>
+    <t>RCM_PT_F2F_ALIPY_NUM</t>
+  </si>
+  <si>
+    <t>支付宝数量（当面付）</t>
+  </si>
+  <si>
+    <t>PT_F2F_ALIPY_NUM</t>
+  </si>
+  <si>
+    <t>标识支付宝数量（当面付）业务信息</t>
+  </si>
+  <si>
+    <t>RCM_PT_F2F_WECHAT_NUM</t>
+  </si>
+  <si>
+    <t>微信支付数量（当面付）</t>
+  </si>
+  <si>
+    <t>PT_F2F_WECHAT_NUM</t>
+  </si>
+  <si>
+    <t>标识微信支付数量（当面付）业务信息</t>
+  </si>
+  <si>
+    <t>RCM_PT_P12_LATEFEE</t>
+  </si>
+  <si>
+    <t>污水费违约金金额</t>
+  </si>
+  <si>
+    <t>PT_P12_LATEFEE</t>
+  </si>
+  <si>
+    <t>记录污水费违约金金额数据</t>
+  </si>
+  <si>
+    <t>RCM_PT_P12_LATEFEE_NUM</t>
+  </si>
+  <si>
+    <t>污水费违约金笔数</t>
+  </si>
+  <si>
+    <t>PT_P12_LATEFEE_NUM</t>
+  </si>
+  <si>
+    <t>记录污水费违约金笔数统计值</t>
+  </si>
+  <si>
+    <t>RCM_PT_IC_MONEY</t>
+  </si>
+  <si>
+    <t>IC卡收费金额</t>
+  </si>
+  <si>
+    <t>PT_IC_MONEY</t>
+  </si>
+  <si>
+    <t>记录IC卡收费金额数据</t>
+  </si>
+  <si>
+    <t>RCM_PT_IC_NUM</t>
+  </si>
+  <si>
+    <t>IC卡收费笔数</t>
+  </si>
+  <si>
+    <t>PT_IC_NUM</t>
+  </si>
+  <si>
+    <t>记录IC卡收费笔数统计值</t>
+  </si>
+  <si>
+    <t>RCM_SUMMONS_NUMBER</t>
+  </si>
+  <si>
+    <t>传票号</t>
+  </si>
+  <si>
+    <t>SUMMONS_NUMBER</t>
+  </si>
+  <si>
+    <t>标识传票号业务信息</t>
+  </si>
+  <si>
+    <t>RCM_SUMMONS_USER</t>
+  </si>
+  <si>
+    <t>传票操作人</t>
+  </si>
+  <si>
+    <t>SUMMONS_USER</t>
+  </si>
+  <si>
+    <t>标识传票操作人业务信息</t>
+  </si>
+  <si>
+    <t>RCM_SUMMONS_TIME</t>
+  </si>
+  <si>
+    <t>传票时间</t>
+  </si>
+  <si>
+    <t>SUMMONS_TIME</t>
+  </si>
+  <si>
+    <t>记录业务传票时间</t>
+  </si>
+  <si>
+    <t>RCM_CHECKOUT_METHOD</t>
+  </si>
+  <si>
+    <t>结账方式</t>
+  </si>
+  <si>
+    <t>CHECKOUT_METHOD</t>
+  </si>
+  <si>
+    <t>标识结账方式业务信息</t>
+  </si>
+  <si>
+    <t>RCM_PT_UNDOPRE_MONEY</t>
+  </si>
+  <si>
+    <t>反预存金额</t>
+  </si>
+  <si>
+    <t>PT_UNDOPRE_MONEY</t>
+  </si>
+  <si>
+    <t>记录反预存金额数据</t>
+  </si>
+  <si>
+    <t>RCM_PT_UNDOPRE_NUM</t>
+  </si>
+  <si>
+    <t>反预存笔数</t>
+  </si>
+  <si>
+    <t>PT_UNDOPRE_NUM</t>
+  </si>
+  <si>
+    <t>记录反预存笔数统计值</t>
   </si>
 </sst>
 </file>
@@ -524,7 +983,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -549,17 +1008,6 @@
       <b/>
       <sz val="9"/>
       <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Microsoft YaHei"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1079,10 +1527,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1091,31 +1539,37 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1124,104 +1578,98 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1233,7 +1681,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1280,9 +1728,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1630,33 +2075,36 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AD20"/>
+  <dimension ref="A1:AD58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="1" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="9" width="28" customWidth="1"/>
+    <col min="8" max="8" width="28" customWidth="1"/>
+    <col min="9" max="9" width="24" customWidth="1"/>
     <col min="10" max="10" width="10" customWidth="1"/>
     <col min="11" max="11" width="12" customWidth="1"/>
     <col min="12" max="12" width="16" customWidth="1"/>
     <col min="13" max="13" width="10" customWidth="1"/>
     <col min="14" max="14" width="14" customWidth="1"/>
-    <col min="15" max="15" width="18" customWidth="1"/>
-    <col min="16" max="19" width="10" customWidth="1"/>
+    <col min="15" max="15" width="20" customWidth="1"/>
+    <col min="16" max="16" width="12" customWidth="1"/>
+    <col min="17" max="19" width="10" customWidth="1"/>
     <col min="20" max="20" width="8" customWidth="1"/>
-    <col min="21" max="21" width="14" customWidth="1"/>
-    <col min="22" max="22" width="18" customWidth="1"/>
+    <col min="21" max="21" width="16" customWidth="1"/>
+    <col min="22" max="22" width="22" customWidth="1"/>
     <col min="23" max="23" width="12" customWidth="1"/>
-    <col min="24" max="24" width="22" customWidth="1"/>
-    <col min="25" max="26" width="14" customWidth="1"/>
-    <col min="27" max="27" width="12" customWidth="1"/>
-    <col min="28" max="28" width="10" customWidth="1"/>
-    <col min="29" max="29" width="14" customWidth="1"/>
+    <col min="24" max="24" width="14.875" customWidth="1"/>
+    <col min="25" max="25" width="27" customWidth="1"/>
+    <col min="26" max="26" width="18" customWidth="1"/>
+    <col min="27" max="27" width="16" customWidth="1"/>
+    <col min="28" max="28" width="12" customWidth="1"/>
+    <col min="29" max="29" width="10" customWidth="1"/>
+    <col min="30" max="30" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="28" customHeight="1" spans="1:30">
@@ -1887,7 +2335,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" ht="33" spans="1:30">
+    <row r="4" ht="27" spans="1:30">
       <c r="A4" s="5" t="s">
         <v>66</v>
       </c>
@@ -1940,7 +2388,7 @@
         <v>79</v>
       </c>
       <c r="R4" s="5">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="S4" s="5">
         <v>0</v>
@@ -1965,27 +2413,27 @@
         <v>84</v>
       </c>
       <c r="AA4" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB4" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="AB4" s="5" t="s">
+      <c r="AC4" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="AC4" s="5" t="s">
+      <c r="AD4" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="AD4" s="5" t="s">
+    </row>
+    <row r="5" ht="27" spans="1:30">
+      <c r="A5" s="5" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="5" ht="33" spans="1:30">
-      <c r="A5" s="5" t="s">
+      <c r="B5" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="C5" s="5" t="s">
         <v>90</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>91</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>69</v>
@@ -2000,10 +2448,10 @@
         <v>72</v>
       </c>
       <c r="H5" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="I5" s="5" t="s">
         <v>92</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>93</v>
       </c>
       <c r="J5" s="5" t="s">
         <v>75</v>
@@ -2024,16 +2472,16 @@
         <v>77</v>
       </c>
       <c r="P5" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q5" s="5" t="s">
         <v>94</v>
-      </c>
-      <c r="Q5" s="5" t="s">
-        <v>95</v>
       </c>
       <c r="R5" s="5">
         <v>10</v>
       </c>
-      <c r="S5" s="5" t="s">
-        <v>75</v>
+      <c r="S5" s="5">
+        <v>0</v>
       </c>
       <c r="T5" s="5" t="s">
         <v>75</v>
@@ -2052,30 +2500,30 @@
         <v>83</v>
       </c>
       <c r="Z5" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="AA5" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="AA5" s="21" t="s">
+      <c r="AB5" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="AB5" s="5" t="s">
+      <c r="AC5" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD5" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" ht="27" spans="1:30">
+      <c r="A6" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="AC5" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="AD5" s="5" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="6" ht="33" spans="1:30">
-      <c r="A6" s="5" t="s">
+      <c r="B6" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="C6" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>69</v>
@@ -2090,10 +2538,10 @@
         <v>72</v>
       </c>
       <c r="H6" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="I6" s="5" t="s">
         <v>102</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>103</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>75</v>
@@ -2120,7 +2568,7 @@
         <v>79</v>
       </c>
       <c r="R6" s="5">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="S6" s="5">
         <v>0</v>
@@ -2145,27 +2593,27 @@
         <v>84</v>
       </c>
       <c r="AA6" s="5" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="AB6" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC6" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="AC6" s="5" t="s">
+      <c r="AD6" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="AD6" s="5" t="s">
-        <v>88</v>
-      </c>
     </row>
-    <row r="7" ht="33" spans="1:30">
+    <row r="7" ht="27" spans="1:30">
       <c r="A7" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="C7" s="5" t="s">
         <v>105</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>106</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>69</v>
@@ -2180,10 +2628,10 @@
         <v>72</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J7" s="5" t="s">
         <v>75</v>
@@ -2210,7 +2658,7 @@
         <v>79</v>
       </c>
       <c r="R7" s="5">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="S7" s="5">
         <v>0</v>
@@ -2235,27 +2683,27 @@
         <v>84</v>
       </c>
       <c r="AA7" s="5" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="AB7" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC7" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="AC7" s="5" t="s">
+      <c r="AD7" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="AD7" s="5" t="s">
-        <v>88</v>
-      </c>
     </row>
-    <row r="8" ht="33" spans="1:30">
+    <row r="8" ht="27" spans="1:30">
       <c r="A8" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="C8" s="5" t="s">
         <v>109</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>110</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>69</v>
@@ -2270,10 +2718,10 @@
         <v>72</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>75</v>
@@ -2294,16 +2742,16 @@
         <v>77</v>
       </c>
       <c r="P8" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q8" s="5" t="s">
         <v>112</v>
-      </c>
-      <c r="Q8" s="5" t="s">
-        <v>113</v>
       </c>
       <c r="R8" s="5">
         <v>7</v>
       </c>
-      <c r="S8" s="5" t="s">
-        <v>75</v>
+      <c r="S8" s="5">
+        <v>0</v>
       </c>
       <c r="T8" s="5" t="s">
         <v>75</v>
@@ -2322,30 +2770,30 @@
         <v>83</v>
       </c>
       <c r="Z8" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA8" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="AA8" s="5" t="s">
+      <c r="AB8" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC8" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD8" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9" ht="27" spans="1:30">
+      <c r="A9" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="AB8" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="AC8" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="AD8" s="5" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="9" ht="33" spans="1:30">
-      <c r="A9" s="5" t="s">
+      <c r="B9" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="C9" s="5" t="s">
         <v>117</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>118</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>69</v>
@@ -2360,10 +2808,10 @@
         <v>72</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>75</v>
@@ -2384,16 +2832,16 @@
         <v>77</v>
       </c>
       <c r="P9" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q9" s="5" t="s">
         <v>112</v>
-      </c>
-      <c r="Q9" s="5" t="s">
-        <v>113</v>
       </c>
       <c r="R9" s="5">
         <v>7</v>
       </c>
-      <c r="S9" s="5" t="s">
-        <v>75</v>
+      <c r="S9" s="5">
+        <v>0</v>
       </c>
       <c r="T9" s="5" t="s">
         <v>75</v>
@@ -2412,30 +2860,30 @@
         <v>83</v>
       </c>
       <c r="Z9" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA9" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="AA9" s="5" t="s">
-        <v>115</v>
-      </c>
       <c r="AB9" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC9" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="AC9" s="5" t="s">
+      <c r="AD9" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="AD9" s="5" t="s">
-        <v>88</v>
-      </c>
     </row>
-    <row r="10" ht="33" spans="1:30">
+    <row r="10" ht="27" spans="1:30">
       <c r="A10" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="C10" s="5" t="s">
         <v>121</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>122</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>69</v>
@@ -2450,10 +2898,10 @@
         <v>72</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>75</v>
@@ -2480,13 +2928,13 @@
         <v>79</v>
       </c>
       <c r="R10" s="5">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="S10" s="5">
         <v>0</v>
       </c>
       <c r="T10" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="U10" s="5" t="s">
         <v>80</v>
@@ -2505,27 +2953,27 @@
         <v>84</v>
       </c>
       <c r="AA10" s="5" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="AB10" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC10" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="AC10" s="5" t="s">
+      <c r="AD10" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="AD10" s="5" t="s">
-        <v>88</v>
-      </c>
     </row>
-    <row r="11" ht="33" spans="1:30">
+    <row r="11" ht="27" spans="1:30">
       <c r="A11" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="C11" s="5" t="s">
         <v>126</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>127</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>69</v>
@@ -2540,10 +2988,10 @@
         <v>72</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J11" s="5" t="s">
         <v>75</v>
@@ -2570,13 +3018,13 @@
         <v>79</v>
       </c>
       <c r="R11" s="5">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="S11" s="5">
         <v>2</v>
       </c>
       <c r="T11" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="U11" s="5" t="s">
         <v>80</v>
@@ -2595,27 +3043,27 @@
         <v>84</v>
       </c>
       <c r="AA11" s="5" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="AB11" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC11" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="AC11" s="5" t="s">
+      <c r="AD11" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="AD11" s="5" t="s">
-        <v>88</v>
-      </c>
     </row>
-    <row r="12" ht="33" spans="1:30">
+    <row r="12" ht="27" spans="1:30">
       <c r="A12" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="C12" s="5" t="s">
         <v>131</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>132</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>69</v>
@@ -2630,10 +3078,10 @@
         <v>72</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J12" s="5" t="s">
         <v>75</v>
@@ -2660,13 +3108,13 @@
         <v>79</v>
       </c>
       <c r="R12" s="5">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="S12" s="5">
         <v>0</v>
       </c>
       <c r="T12" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="U12" s="5" t="s">
         <v>80</v>
@@ -2685,27 +3133,27 @@
         <v>84</v>
       </c>
       <c r="AA12" s="5" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="AB12" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC12" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="AC12" s="5" t="s">
+      <c r="AD12" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="AD12" s="5" t="s">
-        <v>88</v>
-      </c>
     </row>
-    <row r="13" ht="33" spans="1:30">
+    <row r="13" ht="27" spans="1:30">
       <c r="A13" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="C13" s="5" t="s">
         <v>135</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>136</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>69</v>
@@ -2720,10 +3168,10 @@
         <v>72</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J13" s="5" t="s">
         <v>75</v>
@@ -2750,13 +3198,13 @@
         <v>79</v>
       </c>
       <c r="R13" s="5">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="S13" s="5">
         <v>2</v>
       </c>
       <c r="T13" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="U13" s="5" t="s">
         <v>80</v>
@@ -2775,27 +3223,27 @@
         <v>84</v>
       </c>
       <c r="AA13" s="5" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="AB13" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC13" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="AC13" s="5" t="s">
+      <c r="AD13" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="AD13" s="5" t="s">
-        <v>88</v>
-      </c>
     </row>
-    <row r="14" ht="33" spans="1:30">
+    <row r="14" ht="27" spans="1:30">
       <c r="A14" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="C14" s="5" t="s">
         <v>139</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>140</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>69</v>
@@ -2810,10 +3258,10 @@
         <v>72</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J14" s="5" t="s">
         <v>75</v>
@@ -2840,13 +3288,13 @@
         <v>79</v>
       </c>
       <c r="R14" s="5">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="S14" s="5">
         <v>0</v>
       </c>
       <c r="T14" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="U14" s="5" t="s">
         <v>80</v>
@@ -2865,27 +3313,27 @@
         <v>84</v>
       </c>
       <c r="AA14" s="5" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="AB14" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC14" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="AC14" s="5" t="s">
+      <c r="AD14" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="AD14" s="5" t="s">
-        <v>88</v>
-      </c>
     </row>
-    <row r="15" ht="33" spans="1:30">
+    <row r="15" ht="27" spans="1:30">
       <c r="A15" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="C15" s="5" t="s">
         <v>143</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>144</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>69</v>
@@ -2900,10 +3348,10 @@
         <v>72</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J15" s="5" t="s">
         <v>75</v>
@@ -2930,13 +3378,13 @@
         <v>79</v>
       </c>
       <c r="R15" s="5">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="S15" s="5">
         <v>2</v>
       </c>
       <c r="T15" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="U15" s="5" t="s">
         <v>80</v>
@@ -2955,27 +3403,27 @@
         <v>84</v>
       </c>
       <c r="AA15" s="5" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="AB15" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC15" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="AC15" s="5" t="s">
+      <c r="AD15" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="AD15" s="5" t="s">
-        <v>88</v>
-      </c>
     </row>
-    <row r="16" ht="33" spans="1:30">
+    <row r="16" ht="27" spans="1:30">
       <c r="A16" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="C16" s="5" t="s">
         <v>147</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>148</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>69</v>
@@ -2990,10 +3438,10 @@
         <v>72</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J16" s="5" t="s">
         <v>75</v>
@@ -3020,13 +3468,13 @@
         <v>79</v>
       </c>
       <c r="R16" s="5">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="S16" s="5">
         <v>0</v>
       </c>
       <c r="T16" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="U16" s="5" t="s">
         <v>80</v>
@@ -3045,27 +3493,27 @@
         <v>84</v>
       </c>
       <c r="AA16" s="5" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="AB16" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC16" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="AC16" s="5" t="s">
+      <c r="AD16" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="AD16" s="5" t="s">
-        <v>88</v>
-      </c>
     </row>
-    <row r="17" ht="33" spans="1:30">
+    <row r="17" ht="27" spans="1:30">
       <c r="A17" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="C17" s="5" t="s">
         <v>151</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>152</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>69</v>
@@ -3080,10 +3528,10 @@
         <v>72</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J17" s="5" t="s">
         <v>75</v>
@@ -3110,13 +3558,13 @@
         <v>79</v>
       </c>
       <c r="R17" s="5">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="S17" s="5">
         <v>2</v>
       </c>
       <c r="T17" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="U17" s="5" t="s">
         <v>80</v>
@@ -3135,27 +3583,27 @@
         <v>84</v>
       </c>
       <c r="AA17" s="5" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="AB17" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC17" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="AC17" s="5" t="s">
+      <c r="AD17" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="AD17" s="5" t="s">
-        <v>88</v>
-      </c>
     </row>
-    <row r="18" ht="33" spans="1:30">
+    <row r="18" ht="27" spans="1:30">
       <c r="A18" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="C18" s="5" t="s">
         <v>155</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>156</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>69</v>
@@ -3170,10 +3618,10 @@
         <v>72</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J18" s="5" t="s">
         <v>75</v>
@@ -3200,13 +3648,13 @@
         <v>79</v>
       </c>
       <c r="R18" s="5">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="S18" s="5">
         <v>0</v>
       </c>
       <c r="T18" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="U18" s="5" t="s">
         <v>80</v>
@@ -3225,27 +3673,27 @@
         <v>84</v>
       </c>
       <c r="AA18" s="5" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="AB18" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC18" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="AC18" s="5" t="s">
+      <c r="AD18" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="AD18" s="5" t="s">
-        <v>88</v>
-      </c>
     </row>
-    <row r="19" ht="33" spans="1:30">
+    <row r="19" ht="27" spans="1:30">
       <c r="A19" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B19" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="C19" s="5" t="s">
         <v>159</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>160</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>69</v>
@@ -3260,10 +3708,10 @@
         <v>72</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J19" s="5" t="s">
         <v>75</v>
@@ -3290,13 +3738,13 @@
         <v>79</v>
       </c>
       <c r="R19" s="5">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="S19" s="5">
         <v>2</v>
       </c>
       <c r="T19" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="U19" s="5" t="s">
         <v>80</v>
@@ -3315,27 +3763,27 @@
         <v>84</v>
       </c>
       <c r="AA19" s="5" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="AB19" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC19" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="AC19" s="5" t="s">
+      <c r="AD19" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="AD19" s="5" t="s">
-        <v>88</v>
-      </c>
     </row>
-    <row r="20" ht="33" spans="1:30">
+    <row r="20" ht="27" spans="1:30">
       <c r="A20" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="C20" s="5" t="s">
         <v>163</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>164</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>69</v>
@@ -3350,10 +3798,10 @@
         <v>72</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J20" s="5" t="s">
         <v>75</v>
@@ -3380,13 +3828,13 @@
         <v>79</v>
       </c>
       <c r="R20" s="5">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="S20" s="5">
         <v>0</v>
       </c>
       <c r="T20" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="U20" s="5" t="s">
         <v>80</v>
@@ -3405,16 +3853,3436 @@
         <v>84</v>
       </c>
       <c r="AA20" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB20" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC20" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD20" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="21" ht="27" spans="1:30">
+      <c r="A21" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L21" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M21" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N21" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O21" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P21" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q21" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="R21" s="5">
+        <v>12</v>
+      </c>
+      <c r="S21" s="5">
+        <v>2</v>
+      </c>
+      <c r="T21" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="U21" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V21" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W21" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X21" s="5"/>
+      <c r="Y21" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z21" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="AB20" s="5" t="s">
+      <c r="AA21" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB21" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC21" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="AC20" s="5" t="s">
+      <c r="AD21" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="AD20" s="5" t="s">
-        <v>88</v>
+    </row>
+    <row r="22" ht="27" spans="1:30">
+      <c r="A22" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L22" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M22" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N22" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O22" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P22" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q22" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="R22" s="5">
+        <v>11</v>
+      </c>
+      <c r="S22" s="5">
+        <v>0</v>
+      </c>
+      <c r="T22" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="U22" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V22" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W22" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X22" s="5"/>
+      <c r="Y22" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z22" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA22" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB22" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC22" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD22" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="23" ht="27" spans="1:30">
+      <c r="A23" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L23" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M23" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N23" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O23" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P23" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q23" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="R23" s="5">
+        <v>12</v>
+      </c>
+      <c r="S23" s="5">
+        <v>2</v>
+      </c>
+      <c r="T23" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="U23" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V23" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W23" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X23" s="5"/>
+      <c r="Y23" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z23" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA23" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB23" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC23" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD23" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="24" ht="27" spans="1:30">
+      <c r="A24" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L24" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M24" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N24" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O24" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P24" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q24" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="R24" s="5">
+        <v>11</v>
+      </c>
+      <c r="S24" s="5">
+        <v>0</v>
+      </c>
+      <c r="T24" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="U24" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V24" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W24" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X24" s="5"/>
+      <c r="Y24" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z24" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA24" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB24" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC24" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD24" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="25" ht="27" spans="1:30">
+      <c r="A25" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L25" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M25" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N25" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O25" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P25" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q25" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="R25" s="5">
+        <v>12</v>
+      </c>
+      <c r="S25" s="5">
+        <v>2</v>
+      </c>
+      <c r="T25" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="U25" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V25" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W25" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X25" s="5"/>
+      <c r="Y25" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z25" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA25" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB25" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC25" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD25" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="26" ht="27" spans="1:30">
+      <c r="A26" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L26" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M26" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N26" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O26" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P26" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q26" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="R26" s="5">
+        <v>11</v>
+      </c>
+      <c r="S26" s="5">
+        <v>0</v>
+      </c>
+      <c r="T26" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="U26" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V26" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W26" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X26" s="5"/>
+      <c r="Y26" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z26" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA26" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB26" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC26" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD26" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="27" ht="27" spans="1:30">
+      <c r="A27" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L27" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M27" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N27" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O27" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P27" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q27" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="R27" s="5">
+        <v>12</v>
+      </c>
+      <c r="S27" s="5">
+        <v>2</v>
+      </c>
+      <c r="T27" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="U27" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V27" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W27" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X27" s="5"/>
+      <c r="Y27" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z27" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA27" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB27" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC27" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD27" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="28" ht="27" spans="1:30">
+      <c r="A28" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="J28" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K28" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L28" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M28" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N28" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O28" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P28" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q28" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="R28" s="5">
+        <v>11</v>
+      </c>
+      <c r="S28" s="5">
+        <v>0</v>
+      </c>
+      <c r="T28" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="U28" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V28" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W28" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X28" s="5"/>
+      <c r="Y28" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z28" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA28" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB28" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC28" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD28" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="29" ht="27" spans="1:30">
+      <c r="A29" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="J29" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K29" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L29" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M29" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N29" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O29" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P29" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q29" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="R29" s="5">
+        <v>12</v>
+      </c>
+      <c r="S29" s="5">
+        <v>2</v>
+      </c>
+      <c r="T29" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="U29" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V29" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W29" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X29" s="5"/>
+      <c r="Y29" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z29" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA29" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB29" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC29" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD29" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="30" ht="27" spans="1:30">
+      <c r="A30" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="J30" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K30" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L30" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M30" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N30" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O30" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P30" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q30" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="R30" s="5">
+        <v>11</v>
+      </c>
+      <c r="S30" s="5">
+        <v>0</v>
+      </c>
+      <c r="T30" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="U30" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V30" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W30" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X30" s="5"/>
+      <c r="Y30" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z30" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA30" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB30" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC30" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD30" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="31" ht="27" spans="1:30">
+      <c r="A31" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="J31" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K31" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L31" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M31" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N31" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O31" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P31" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q31" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="R31" s="5">
+        <v>12</v>
+      </c>
+      <c r="S31" s="5">
+        <v>2</v>
+      </c>
+      <c r="T31" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="U31" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V31" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W31" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X31" s="5"/>
+      <c r="Y31" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z31" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA31" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB31" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC31" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD31" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="32" ht="27" spans="1:30">
+      <c r="A32" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="I32" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="J32" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K32" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L32" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M32" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N32" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O32" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P32" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q32" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="R32" s="5">
+        <v>11</v>
+      </c>
+      <c r="S32" s="5">
+        <v>0</v>
+      </c>
+      <c r="T32" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="U32" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V32" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W32" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X32" s="5"/>
+      <c r="Y32" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z32" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA32" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB32" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC32" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD32" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="33" ht="27" spans="1:30">
+      <c r="A33" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="J33" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K33" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L33" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M33" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N33" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O33" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P33" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q33" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="R33" s="5">
+        <v>12</v>
+      </c>
+      <c r="S33" s="5">
+        <v>2</v>
+      </c>
+      <c r="T33" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="U33" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V33" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W33" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X33" s="5"/>
+      <c r="Y33" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z33" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA33" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB33" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC33" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD33" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="34" ht="27" spans="1:30">
+      <c r="A34" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H34" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="J34" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K34" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L34" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M34" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N34" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O34" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P34" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q34" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="R34" s="5">
+        <v>11</v>
+      </c>
+      <c r="S34" s="5">
+        <v>0</v>
+      </c>
+      <c r="T34" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="U34" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V34" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W34" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X34" s="5"/>
+      <c r="Y34" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z34" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA34" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB34" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC34" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD34" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="35" ht="27" spans="1:30">
+      <c r="A35" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="I35" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="J35" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K35" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L35" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M35" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N35" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O35" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P35" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q35" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="R35" s="5">
+        <v>12</v>
+      </c>
+      <c r="S35" s="5">
+        <v>2</v>
+      </c>
+      <c r="T35" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="U35" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V35" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W35" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X35" s="5"/>
+      <c r="Y35" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z35" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA35" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB35" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC35" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD35" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="36" ht="27" spans="1:30">
+      <c r="A36" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H36" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="J36" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K36" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L36" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M36" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N36" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O36" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P36" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q36" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="R36" s="5">
+        <v>11</v>
+      </c>
+      <c r="S36" s="5">
+        <v>0</v>
+      </c>
+      <c r="T36" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="U36" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V36" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W36" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X36" s="5"/>
+      <c r="Y36" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z36" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA36" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB36" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC36" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD36" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="37" ht="27" spans="1:30">
+      <c r="A37" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H37" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="J37" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K37" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L37" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M37" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N37" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O37" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P37" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q37" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="R37" s="5">
+        <v>12</v>
+      </c>
+      <c r="S37" s="5">
+        <v>2</v>
+      </c>
+      <c r="T37" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="U37" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V37" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W37" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X37" s="5"/>
+      <c r="Y37" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z37" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA37" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB37" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC37" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD37" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="38" ht="27" spans="1:30">
+      <c r="A38" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H38" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="I38" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="J38" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K38" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L38" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M38" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N38" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O38" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P38" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q38" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="R38" s="5">
+        <v>11</v>
+      </c>
+      <c r="S38" s="5">
+        <v>0</v>
+      </c>
+      <c r="T38" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="U38" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V38" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W38" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X38" s="5"/>
+      <c r="Y38" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z38" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA38" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="AB38" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC38" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD38" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="39" ht="27" spans="1:30">
+      <c r="A39" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H39" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="I39" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="J39" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K39" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L39" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M39" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N39" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O39" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P39" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q39" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="R39" s="5">
+        <v>7</v>
+      </c>
+      <c r="S39" s="5">
+        <v>0</v>
+      </c>
+      <c r="T39" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="U39" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V39" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W39" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X39" s="5"/>
+      <c r="Y39" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z39" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA39" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="AB39" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="AC39" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD39" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="40" ht="27" spans="1:30">
+      <c r="A40" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H40" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="J40" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K40" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L40" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M40" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N40" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O40" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P40" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q40" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="R40" s="5">
+        <v>11</v>
+      </c>
+      <c r="S40" s="5">
+        <v>0</v>
+      </c>
+      <c r="T40" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="U40" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V40" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W40" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X40" s="5"/>
+      <c r="Y40" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z40" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA40" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB40" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="AC40" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD40" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="41" ht="27" spans="1:30">
+      <c r="A41" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="J41" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K41" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L41" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M41" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N41" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O41" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P41" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q41" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="R41" s="5">
+        <v>7</v>
+      </c>
+      <c r="S41" s="5">
+        <v>0</v>
+      </c>
+      <c r="T41" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="U41" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V41" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W41" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X41" s="5"/>
+      <c r="Y41" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z41" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA41" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="AB41" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="AC41" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD41" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="42" ht="27" spans="1:30">
+      <c r="A42" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H42" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="I42" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="J42" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K42" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L42" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M42" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N42" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O42" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P42" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q42" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="R42" s="5">
+        <v>11</v>
+      </c>
+      <c r="S42" s="5">
+        <v>0</v>
+      </c>
+      <c r="T42" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="U42" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V42" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W42" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X42" s="5"/>
+      <c r="Y42" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z42" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA42" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB42" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="AC42" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD42" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="43" ht="27" spans="1:30">
+      <c r="A43" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H43" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="J43" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K43" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L43" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M43" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N43" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O43" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P43" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q43" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="R43" s="5">
+        <v>7</v>
+      </c>
+      <c r="S43" s="5">
+        <v>0</v>
+      </c>
+      <c r="T43" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="U43" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V43" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W43" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X43" s="5"/>
+      <c r="Y43" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z43" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA43" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="AB43" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="AC43" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD43" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="44" ht="27" spans="1:30">
+      <c r="A44" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H44" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="J44" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K44" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L44" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M44" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N44" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O44" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P44" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q44" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="R44" s="5">
+        <v>7</v>
+      </c>
+      <c r="S44" s="5">
+        <v>0</v>
+      </c>
+      <c r="T44" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="U44" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V44" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W44" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X44" s="5"/>
+      <c r="Y44" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z44" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA44" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="AB44" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="AC44" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD44" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="45" ht="27" spans="1:30">
+      <c r="A45" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H45" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="I45" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="J45" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K45" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L45" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M45" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N45" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O45" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P45" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q45" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="R45" s="5">
+        <v>12</v>
+      </c>
+      <c r="S45" s="5">
+        <v>2</v>
+      </c>
+      <c r="T45" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="U45" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V45" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W45" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X45" s="5"/>
+      <c r="Y45" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z45" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA45" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB45" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC45" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD45" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="46" ht="27" spans="1:30">
+      <c r="A46" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H46" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="I46" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="J46" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K46" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L46" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M46" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N46" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O46" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P46" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q46" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="R46" s="5">
+        <v>12</v>
+      </c>
+      <c r="S46" s="5">
+        <v>2</v>
+      </c>
+      <c r="T46" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="U46" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V46" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W46" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X46" s="5"/>
+      <c r="Y46" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z46" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA46" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB46" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC46" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD46" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="47" ht="27" spans="1:30">
+      <c r="A47" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H47" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="I47" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="J47" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K47" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L47" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M47" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N47" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O47" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P47" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q47" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="R47" s="5">
+        <v>11</v>
+      </c>
+      <c r="S47" s="5">
+        <v>0</v>
+      </c>
+      <c r="T47" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="U47" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V47" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W47" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X47" s="5"/>
+      <c r="Y47" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z47" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA47" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB47" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="AC47" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD47" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="48" ht="27" spans="1:30">
+      <c r="A48" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H48" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="I48" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="J48" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K48" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L48" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M48" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N48" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O48" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P48" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q48" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="R48" s="5">
+        <v>11</v>
+      </c>
+      <c r="S48" s="5">
+        <v>0</v>
+      </c>
+      <c r="T48" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="U48" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V48" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W48" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X48" s="5"/>
+      <c r="Y48" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z48" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA48" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB48" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="AC48" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD48" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="49" ht="27" spans="1:30">
+      <c r="A49" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H49" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="I49" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="J49" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K49" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L49" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M49" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N49" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O49" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P49" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q49" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="R49" s="5">
+        <v>12</v>
+      </c>
+      <c r="S49" s="5">
+        <v>2</v>
+      </c>
+      <c r="T49" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="U49" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V49" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W49" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X49" s="5"/>
+      <c r="Y49" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z49" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA49" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB49" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="AC49" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD49" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="50" ht="27" spans="1:30">
+      <c r="A50" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H50" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="I50" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="J50" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K50" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L50" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M50" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N50" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O50" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P50" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q50" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="R50" s="5">
+        <v>11</v>
+      </c>
+      <c r="S50" s="5">
+        <v>0</v>
+      </c>
+      <c r="T50" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="U50" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V50" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W50" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X50" s="5"/>
+      <c r="Y50" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z50" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA50" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB50" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="AC50" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD50" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="51" ht="27" spans="1:30">
+      <c r="A51" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F51" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H51" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="I51" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="J51" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K51" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L51" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M51" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N51" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O51" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P51" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q51" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="R51" s="5">
+        <v>12</v>
+      </c>
+      <c r="S51" s="5">
+        <v>2</v>
+      </c>
+      <c r="T51" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="U51" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V51" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W51" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X51" s="5"/>
+      <c r="Y51" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z51" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA51" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB51" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="AC51" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD51" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="52" ht="27" spans="1:30">
+      <c r="A52" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F52" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G52" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H52" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="I52" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="J52" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K52" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L52" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M52" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N52" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O52" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P52" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q52" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="R52" s="5">
+        <v>11</v>
+      </c>
+      <c r="S52" s="5">
+        <v>0</v>
+      </c>
+      <c r="T52" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="U52" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V52" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W52" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X52" s="5"/>
+      <c r="Y52" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z52" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA52" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB52" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="AC52" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD52" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="53" ht="27" spans="1:30">
+      <c r="A53" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F53" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H53" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="I53" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="J53" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K53" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L53" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M53" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N53" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O53" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P53" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q53" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="R53" s="5">
+        <v>200</v>
+      </c>
+      <c r="S53" s="5">
+        <v>0</v>
+      </c>
+      <c r="T53" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="U53" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V53" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W53" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X53" s="5"/>
+      <c r="Y53" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z53" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="AA53" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="AB53" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="AC53" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD53" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="54" ht="27" spans="1:30">
+      <c r="A54" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F54" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H54" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="I54" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="J54" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K54" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L54" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M54" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N54" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O54" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P54" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q54" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="R54" s="5">
+        <v>10</v>
+      </c>
+      <c r="S54" s="5">
+        <v>0</v>
+      </c>
+      <c r="T54" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="U54" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V54" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W54" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X54" s="5"/>
+      <c r="Y54" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z54" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA54" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB54" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="AC54" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD54" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="55" ht="27" spans="1:30">
+      <c r="A55" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F55" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H55" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="I55" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="J55" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K55" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L55" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M55" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N55" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O55" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P55" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q55" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="R55" s="5">
+        <v>7</v>
+      </c>
+      <c r="S55" s="5">
+        <v>0</v>
+      </c>
+      <c r="T55" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="U55" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V55" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W55" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X55" s="5"/>
+      <c r="Y55" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z55" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA55" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="AB55" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="AC55" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD55" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="56" ht="27" spans="1:30">
+      <c r="A56" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F56" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G56" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H56" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="I56" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="J56" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K56" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L56" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M56" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N56" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O56" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P56" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q56" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="R56" s="5">
+        <v>10</v>
+      </c>
+      <c r="S56" s="5">
+        <v>0</v>
+      </c>
+      <c r="T56" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="U56" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V56" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W56" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X56" s="5"/>
+      <c r="Y56" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z56" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA56" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB56" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="AC56" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD56" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="57" ht="27" spans="1:30">
+      <c r="A57" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F57" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G57" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H57" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="I57" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="J57" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K57" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L57" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M57" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N57" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O57" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P57" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q57" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="R57" s="5">
+        <v>18</v>
+      </c>
+      <c r="S57" s="5">
+        <v>4</v>
+      </c>
+      <c r="T57" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="U57" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V57" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W57" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X57" s="5"/>
+      <c r="Y57" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z57" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA57" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB57" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="AC57" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD57" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="58" ht="27" spans="1:30">
+      <c r="A58" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F58" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H58" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="I58" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="J58" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K58" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L58" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M58" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N58" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O58" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P58" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q58" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="R58" s="5">
+        <v>11</v>
+      </c>
+      <c r="S58" s="5">
+        <v>0</v>
+      </c>
+      <c r="T58" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="U58" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V58" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W58" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X58" s="5"/>
+      <c r="Y58" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z58" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA58" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB58" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="AC58" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD58" s="5" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/dama/cases/营收系统数据标准/2 服务类/2.4 业务交易数据/2.4.2 收费信息/14. 收费汇总.xlsx
+++ b/dama/cases/营收系统数据标准/2 服务类/2.4 业务交易数据/2.4.2 收费信息/14. 收费汇总.xlsx
@@ -2388,7 +2388,7 @@
         <v>79</v>
       </c>
       <c r="R4" s="5">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="S4" s="5">
         <v>0</v>
@@ -2568,7 +2568,7 @@
         <v>79</v>
       </c>
       <c r="R6" s="5">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="S6" s="5">
         <v>0</v>
@@ -2658,7 +2658,7 @@
         <v>79</v>
       </c>
       <c r="R7" s="5">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="S7" s="5">
         <v>0</v>
@@ -2928,7 +2928,7 @@
         <v>79</v>
       </c>
       <c r="R10" s="5">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="S10" s="5">
         <v>0</v>
@@ -3018,7 +3018,7 @@
         <v>79</v>
       </c>
       <c r="R11" s="5">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="S11" s="5">
         <v>2</v>
@@ -3108,7 +3108,7 @@
         <v>79</v>
       </c>
       <c r="R12" s="5">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="S12" s="5">
         <v>0</v>
@@ -3198,7 +3198,7 @@
         <v>79</v>
       </c>
       <c r="R13" s="5">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="S13" s="5">
         <v>2</v>
@@ -3288,7 +3288,7 @@
         <v>79</v>
       </c>
       <c r="R14" s="5">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="S14" s="5">
         <v>0</v>
@@ -3378,7 +3378,7 @@
         <v>79</v>
       </c>
       <c r="R15" s="5">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="S15" s="5">
         <v>2</v>
@@ -3468,7 +3468,7 @@
         <v>79</v>
       </c>
       <c r="R16" s="5">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="S16" s="5">
         <v>0</v>
@@ -3558,7 +3558,7 @@
         <v>79</v>
       </c>
       <c r="R17" s="5">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="S17" s="5">
         <v>2</v>
@@ -3648,7 +3648,7 @@
         <v>79</v>
       </c>
       <c r="R18" s="5">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="S18" s="5">
         <v>0</v>
@@ -3738,7 +3738,7 @@
         <v>79</v>
       </c>
       <c r="R19" s="5">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="S19" s="5">
         <v>2</v>
@@ -3828,7 +3828,7 @@
         <v>79</v>
       </c>
       <c r="R20" s="5">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="S20" s="5">
         <v>0</v>
@@ -3918,7 +3918,7 @@
         <v>79</v>
       </c>
       <c r="R21" s="5">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="S21" s="5">
         <v>2</v>
@@ -4008,7 +4008,7 @@
         <v>79</v>
       </c>
       <c r="R22" s="5">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="S22" s="5">
         <v>0</v>
@@ -4098,7 +4098,7 @@
         <v>79</v>
       </c>
       <c r="R23" s="5">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="S23" s="5">
         <v>2</v>
@@ -4188,7 +4188,7 @@
         <v>79</v>
       </c>
       <c r="R24" s="5">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="S24" s="5">
         <v>0</v>
@@ -4278,7 +4278,7 @@
         <v>79</v>
       </c>
       <c r="R25" s="5">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="S25" s="5">
         <v>2</v>
@@ -4368,7 +4368,7 @@
         <v>79</v>
       </c>
       <c r="R26" s="5">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="S26" s="5">
         <v>0</v>
@@ -4458,7 +4458,7 @@
         <v>79</v>
       </c>
       <c r="R27" s="5">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="S27" s="5">
         <v>2</v>
@@ -4548,7 +4548,7 @@
         <v>79</v>
       </c>
       <c r="R28" s="5">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="S28" s="5">
         <v>0</v>
@@ -4638,7 +4638,7 @@
         <v>79</v>
       </c>
       <c r="R29" s="5">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="S29" s="5">
         <v>2</v>
@@ -4728,7 +4728,7 @@
         <v>79</v>
       </c>
       <c r="R30" s="5">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="S30" s="5">
         <v>0</v>
@@ -4818,7 +4818,7 @@
         <v>79</v>
       </c>
       <c r="R31" s="5">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="S31" s="5">
         <v>2</v>
@@ -4908,7 +4908,7 @@
         <v>79</v>
       </c>
       <c r="R32" s="5">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="S32" s="5">
         <v>0</v>
@@ -4998,7 +4998,7 @@
         <v>79</v>
       </c>
       <c r="R33" s="5">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="S33" s="5">
         <v>2</v>
@@ -5088,7 +5088,7 @@
         <v>79</v>
       </c>
       <c r="R34" s="5">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="S34" s="5">
         <v>0</v>
@@ -5178,7 +5178,7 @@
         <v>79</v>
       </c>
       <c r="R35" s="5">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="S35" s="5">
         <v>2</v>
@@ -5268,7 +5268,7 @@
         <v>79</v>
       </c>
       <c r="R36" s="5">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="S36" s="5">
         <v>0</v>
@@ -5358,7 +5358,7 @@
         <v>79</v>
       </c>
       <c r="R37" s="5">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="S37" s="5">
         <v>2</v>
@@ -5448,7 +5448,7 @@
         <v>79</v>
       </c>
       <c r="R38" s="5">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="S38" s="5">
         <v>0</v>
@@ -5628,7 +5628,7 @@
         <v>79</v>
       </c>
       <c r="R40" s="5">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="S40" s="5">
         <v>0</v>
@@ -5808,7 +5808,7 @@
         <v>79</v>
       </c>
       <c r="R42" s="5">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="S42" s="5">
         <v>0</v>
@@ -6078,7 +6078,7 @@
         <v>79</v>
       </c>
       <c r="R45" s="5">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="S45" s="5">
         <v>2</v>
@@ -6168,7 +6168,7 @@
         <v>79</v>
       </c>
       <c r="R46" s="5">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="S46" s="5">
         <v>2</v>
@@ -6258,7 +6258,7 @@
         <v>79</v>
       </c>
       <c r="R47" s="5">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="S47" s="5">
         <v>0</v>
@@ -6348,7 +6348,7 @@
         <v>79</v>
       </c>
       <c r="R48" s="5">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="S48" s="5">
         <v>0</v>
@@ -6438,7 +6438,7 @@
         <v>79</v>
       </c>
       <c r="R49" s="5">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="S49" s="5">
         <v>2</v>
@@ -6528,7 +6528,7 @@
         <v>79</v>
       </c>
       <c r="R50" s="5">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="S50" s="5">
         <v>0</v>
@@ -6618,7 +6618,7 @@
         <v>79</v>
       </c>
       <c r="R51" s="5">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="S51" s="5">
         <v>2</v>
@@ -6708,7 +6708,7 @@
         <v>79</v>
       </c>
       <c r="R52" s="5">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="S52" s="5">
         <v>0</v>
@@ -7248,7 +7248,7 @@
         <v>79</v>
       </c>
       <c r="R58" s="5">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="S58" s="5">
         <v>0</v>
